--- a/data/trans_dic/P1001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 14,36</t>
+          <t>6,97; 14,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,2</t>
+          <t>7,04; 14,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 21,13</t>
+          <t>12,24; 20,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,7</t>
+          <t>1,1; 5,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 16,69</t>
+          <t>8,35; 16,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 26,96</t>
+          <t>16,96; 26,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 30,9</t>
+          <t>20,81; 31,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,86</t>
+          <t>2,23; 5,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 14,18</t>
+          <t>8,71; 14,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 19,11</t>
+          <t>13,13; 19,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 24,37</t>
+          <t>17,69; 24,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,48</t>
+          <t>2,02; 4,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,2</t>
+          <t>6,09; 11,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 11,13</t>
+          <t>5,6; 10,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,7</t>
+          <t>1,56; 4,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,7</t>
+          <t>5,24; 11,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 18,48</t>
+          <t>11,97; 18,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,93; 18,92</t>
+          <t>12,03; 18,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 12,24</t>
+          <t>7,25; 12,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,69; 13,7</t>
+          <t>8,9; 13,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 13,8</t>
+          <t>9,88; 13,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 13,91</t>
+          <t>9,79; 13,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,84</t>
+          <t>4,74; 7,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,31</t>
+          <t>7,64; 11,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,08</t>
+          <t>1,15; 5,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,4</t>
+          <t>3,09; 8,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,22</t>
+          <t>0,94; 4,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,74</t>
+          <t>3,44; 7,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,2</t>
+          <t>2,09; 6,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 14,81</t>
+          <t>7,71; 14,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,42</t>
+          <t>3,44; 8,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,03</t>
+          <t>6,32; 10,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,85</t>
+          <t>1,88; 4,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,76</t>
+          <t>6,21; 10,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,73</t>
+          <t>2,58; 5,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,55</t>
+          <t>5,36; 8,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,89</t>
+          <t>1,28; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,48</t>
+          <t>3,27; 8,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 12,35</t>
+          <t>6,38; 12,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,94</t>
+          <t>3,62; 9,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,03</t>
+          <t>5,28; 10,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 25,25</t>
+          <t>17,33; 25,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 25,45</t>
+          <t>16,78; 25,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,73</t>
+          <t>5,72; 13,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,03</t>
+          <t>3,62; 6,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 16,21</t>
+          <t>11,22; 16,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,73</t>
+          <t>12,48; 18,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,6</t>
+          <t>5,64; 10,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 10,38</t>
+          <t>3,87; 10,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,5</t>
+          <t>2,47; 8,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,16</t>
+          <t>2,33; 8,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,62</t>
+          <t>1,6; 5,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 12,02</t>
+          <t>3,89; 11,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,23; 24,19</t>
+          <t>13,27; 24,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 11,8</t>
+          <t>4,67; 12,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,04</t>
+          <t>7,22; 12,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,31</t>
+          <t>4,79; 9,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 15,19</t>
+          <t>8,83; 14,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,59</t>
+          <t>4,15; 9,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,45</t>
+          <t>5,03; 8,51</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,68</t>
+          <t>0,32; 3,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,47; 12,11</t>
+          <t>5,08; 12,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 11,36</t>
+          <t>4,35; 10,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,42</t>
+          <t>3,64; 8,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,45</t>
+          <t>2,59; 7,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 15,75</t>
+          <t>8,03; 15,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 18,6</t>
+          <t>10,17; 19,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 11,08</t>
+          <t>6,21; 11,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,54</t>
+          <t>1,66; 4,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,24</t>
+          <t>7,72; 12,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 14,22</t>
+          <t>8,23; 13,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,0</t>
+          <t>5,42; 9,03</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,68</t>
+          <t>4,01; 7,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,45</t>
+          <t>3,37; 7,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,02</t>
+          <t>4,77; 8,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,32</t>
+          <t>6,58; 12,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,0; 13,17</t>
+          <t>8,38; 13,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,56</t>
+          <t>5,93; 10,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,84</t>
+          <t>10,31; 15,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 16,34</t>
+          <t>5,6; 16,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 9,8</t>
+          <t>6,77; 9,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,0</t>
+          <t>5,25; 8,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,8</t>
+          <t>8,21; 11,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 12,82</t>
+          <t>6,39; 12,91</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,3</t>
+          <t>6,34; 10,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,46</t>
+          <t>6,68; 11,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,63</t>
+          <t>2,8; 5,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,59</t>
+          <t>1,98; 6,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,81</t>
+          <t>7,75; 12,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,54; 18,87</t>
+          <t>13,56; 18,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,9</t>
+          <t>6,24; 10,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,73; 18,86</t>
+          <t>13,94; 18,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,55</t>
+          <t>7,6; 10,59</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,58</t>
+          <t>10,99; 14,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,52</t>
+          <t>5,0; 7,53</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,69</t>
+          <t>5,84; 11,85</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,87</t>
+          <t>5,25; 6,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,09</t>
+          <t>6,18; 8,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,96</t>
+          <t>5,3; 6,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,68</t>
+          <t>4,36; 6,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,5</t>
+          <t>8,45; 10,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,51; 15,92</t>
+          <t>13,52; 15,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,11; 13,29</t>
+          <t>11,03; 13,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,89; 11,93</t>
+          <t>8,83; 12,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,42</t>
+          <t>7,14; 8,38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,17; 11,69</t>
+          <t>10,18; 11,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 9,89</t>
+          <t>8,58; 9,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,2</t>
+          <t>7,22; 9,17</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18326; 39209</t>
+          <t>19017; 39135</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20358; 41851</t>
+          <t>20764; 41254</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35583; 62070</t>
+          <t>35942; 61625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3473; 14633</t>
+          <t>3431; 15864</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21253; 43543</t>
+          <t>21771; 43848</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48652; 77436</t>
+          <t>48729; 76374</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60408; 89210</t>
+          <t>60074; 90470</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6402; 16977</t>
+          <t>6458; 16862</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46686; 75679</t>
+          <t>46502; 75045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75429; 111204</t>
+          <t>76416; 112638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100714; 141965</t>
+          <t>103044; 141241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11509; 26927</t>
+          <t>12138; 27210</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29387; 55242</t>
+          <t>30028; 54816</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29007; 56273</t>
+          <t>28324; 55310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8240; 23617</t>
+          <t>7854; 23662</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27957; 55475</t>
+          <t>27187; 58071</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61797; 93140</t>
+          <t>60335; 93561</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62377; 98897</t>
+          <t>62880; 97674</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36207; 64007</t>
+          <t>37920; 63879</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44760; 70572</t>
+          <t>45821; 69572</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96490; 137630</t>
+          <t>98527; 139048</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97988; 143055</t>
+          <t>100639; 143590</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49269; 80362</t>
+          <t>48642; 79793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79339; 116884</t>
+          <t>78900; 115647</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3244; 16187</t>
+          <t>3678; 17017</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10617; 27216</t>
+          <t>10008; 26910</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2801; 13431</t>
+          <t>3006; 12899</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10355; 24478</t>
+          <t>10858; 24320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7080; 20797</t>
+          <t>7024; 22353</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26705; 50520</t>
+          <t>26289; 50486</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11169; 28305</t>
+          <t>11580; 28763</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21217; 38433</t>
+          <t>22035; 37702</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12651; 31720</t>
+          <t>12314; 29868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41929; 71559</t>
+          <t>41326; 70753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16835; 37515</t>
+          <t>16864; 36185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35889; 56802</t>
+          <t>35618; 56188</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4493; 17523</t>
+          <t>4605; 17203</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12873; 31727</t>
+          <t>12220; 30206</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24111; 45688</t>
+          <t>23599; 45764</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10840; 27824</t>
+          <t>11256; 30000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19621; 40963</t>
+          <t>19598; 39843</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66499; 98191</t>
+          <t>67414; 100241</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63458; 98561</t>
+          <t>64976; 97642</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24894; 60547</t>
+          <t>27214; 62246</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27702; 51308</t>
+          <t>26442; 50436</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86261; 123696</t>
+          <t>85567; 124153</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93465; 134237</t>
+          <t>94535; 136371</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44831; 83411</t>
+          <t>44416; 82225</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7965; 21110</t>
+          <t>7874; 20988</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5071; 18067</t>
+          <t>5251; 18258</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4888; 17243</t>
+          <t>4922; 17021</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2873; 10039</t>
+          <t>2851; 9798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8262; 24965</t>
+          <t>8080; 24266</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29061; 53129</t>
+          <t>29131; 52860</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9481; 25794</t>
+          <t>10216; 26769</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14849; 27137</t>
+          <t>15027; 26708</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18930; 38270</t>
+          <t>19679; 40276</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38164; 65666</t>
+          <t>38152; 64026</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17871; 36926</t>
+          <t>17857; 39438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19706; 32667</t>
+          <t>19442; 32906</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>884; 9967</t>
+          <t>878; 8586</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14938; 33052</t>
+          <t>13868; 33110</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11608; 29889</t>
+          <t>11450; 28655</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9607; 22715</t>
+          <t>9816; 22299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6234; 20716</t>
+          <t>7206; 21196</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21552; 44108</t>
+          <t>22480; 43232</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26480; 50813</t>
+          <t>27778; 53284</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16115; 28482</t>
+          <t>15971; 28424</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9224; 24915</t>
+          <t>9129; 25032</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40556; 67709</t>
+          <t>42703; 69411</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43752; 76246</t>
+          <t>44131; 74585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29804; 47423</t>
+          <t>28539; 47585</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24745; 47220</t>
+          <t>24653; 47980</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23335; 49352</t>
+          <t>22361; 46791</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30303; 59195</t>
+          <t>31344; 58810</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41467; 76886</t>
+          <t>41095; 76524</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51068; 84027</t>
+          <t>53491; 83488</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42339; 73203</t>
+          <t>41081; 71209</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72449; 109507</t>
+          <t>71268; 107942</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47229; 138696</t>
+          <t>47526; 138093</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>83817; 122836</t>
+          <t>84836; 121550</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70396; 108508</t>
+          <t>71194; 109064</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>111219; 159005</t>
+          <t>110681; 155345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>96147; 188790</t>
+          <t>94151; 190111</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47321; 76604</t>
+          <t>47180; 77524</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>52581; 89162</t>
+          <t>51950; 89055</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22601; 43840</t>
+          <t>21806; 42576</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16011; 61187</t>
+          <t>18381; 61059</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>59086; 92523</t>
+          <t>60741; 94242</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>111566; 155491</t>
+          <t>111715; 156397</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49649; 81750</t>
+          <t>51524; 84339</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>98450; 135232</t>
+          <t>99945; 133757</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>114909; 161149</t>
+          <t>116097; 161818</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>175993; 233581</t>
+          <t>176028; 235362</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>80851; 120709</t>
+          <t>80192; 120904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>96436; 192393</t>
+          <t>96040; 194995</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>172453; 225005</t>
+          <t>171962; 228714</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>213601; 277081</t>
+          <t>211723; 274717</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>181184; 236112</t>
+          <t>179888; 236610</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153091; 230943</t>
+          <t>150804; 230107</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>283244; 354868</t>
+          <t>285475; 353205</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>480563; 566098</t>
+          <t>480889; 568669</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>393719; 471155</t>
+          <t>390919; 475836</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>325389; 436584</t>
+          <t>323034; 440327</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>472859; 560462</t>
+          <t>475327; 557935</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>709853; 815980</t>
+          <t>710869; 817586</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>592027; 686199</t>
+          <t>595029; 687165</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>516011; 654703</t>
+          <t>514146; 652784</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 14,33</t>
+          <t>7,14; 14,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 14,0</t>
+          <t>7,39; 14,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 20,98</t>
+          <t>12,25; 20,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,09</t>
+          <t>0,85; 4,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,81</t>
+          <t>8,06; 16,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 26,59</t>
+          <t>16,79; 27,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 31,34</t>
+          <t>20,54; 31,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,82</t>
+          <t>2,14; 5,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 14,06</t>
+          <t>8,2; 13,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 19,35</t>
+          <t>12,92; 19,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 24,25</t>
+          <t>17,92; 24,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,53</t>
+          <t>1,91; 4,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,12</t>
+          <t>5,96; 11,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,94</t>
+          <t>5,68; 10,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,71</t>
+          <t>1,65; 4,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,2</t>
+          <t>5,48; 10,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 18,57</t>
+          <t>12,22; 18,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,03; 18,69</t>
+          <t>12,2; 18,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,21</t>
+          <t>6,87; 12,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 13,51</t>
+          <t>8,47; 13,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 13,95</t>
+          <t>9,91; 13,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,96</t>
+          <t>9,84; 13,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,78</t>
+          <t>4,76; 8,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,19</t>
+          <t>7,56; 11,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,34</t>
+          <t>0,92; 4,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,3</t>
+          <t>3,03; 8,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,05</t>
+          <t>0,94; 4,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,69</t>
+          <t>3,6; 8,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,66</t>
+          <t>2,13; 6,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,8</t>
+          <t>7,85; 14,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,55</t>
+          <t>3,41; 8,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,82</t>
+          <t>6,27; 11,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,57</t>
+          <t>1,93; 4,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,64</t>
+          <t>6,03; 10,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,53</t>
+          <t>2,45; 5,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,45</t>
+          <t>5,74; 8,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,8</t>
+          <t>1,35; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,08</t>
+          <t>3,49; 8,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 12,37</t>
+          <t>6,43; 12,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,64</t>
+          <t>3,39; 8,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 10,73</t>
+          <t>5,28; 10,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 25,77</t>
+          <t>17,56; 25,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 25,21</t>
+          <t>16,84; 25,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 13,08</t>
+          <t>8,91; 15,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,91</t>
+          <t>3,71; 7,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,27</t>
+          <t>11,25; 16,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 18,01</t>
+          <t>12,36; 17,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,45</t>
+          <t>6,89; 11,18</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,32</t>
+          <t>3,78; 10,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,59</t>
+          <t>2,47; 8,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,06</t>
+          <t>2,34; 7,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,48</t>
+          <t>1,43; 4,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 11,69</t>
+          <t>4,35; 11,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,27; 24,07</t>
+          <t>13,32; 24,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,25</t>
+          <t>4,51; 11,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 12,84</t>
+          <t>6,77; 11,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,8</t>
+          <t>4,77; 9,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 14,81</t>
+          <t>8,83; 15,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,18</t>
+          <t>4,0; 8,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,51</t>
+          <t>4,64; 7,77</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,17</t>
+          <t>0,35; 3,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,13</t>
+          <t>5,28; 12,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,89</t>
+          <t>4,54; 11,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,27</t>
+          <t>3,45; 8,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,62</t>
+          <t>2,34; 7,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,03; 15,44</t>
+          <t>8,02; 15,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,17; 19,51</t>
+          <t>10,01; 19,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,06</t>
+          <t>6,14; 11,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,56</t>
+          <t>1,77; 4,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,55</t>
+          <t>7,4; 12,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,91</t>
+          <t>8,21; 13,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,03</t>
+          <t>5,42; 8,64</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,8</t>
+          <t>3,88; 7,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,06</t>
+          <t>3,4; 7,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,96</t>
+          <t>4,69; 8,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,26</t>
+          <t>6,21; 11,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,08</t>
+          <t>8,41; 12,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 10,28</t>
+          <t>6,12; 10,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,31; 15,61</t>
+          <t>10,19; 15,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,6; 16,27</t>
+          <t>12,87; 17,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,7</t>
+          <t>6,68; 9,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,04</t>
+          <t>5,22; 8,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,53</t>
+          <t>8,15; 11,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 12,91</t>
+          <t>10,5; 13,87</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,42</t>
+          <t>6,36; 10,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,44</t>
+          <t>6,96; 11,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,47</t>
+          <t>2,79; 5,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,57</t>
+          <t>4,33; 7,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,03</t>
+          <t>7,75; 11,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,56; 18,98</t>
+          <t>13,51; 18,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,21</t>
+          <t>6,13; 10,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,94; 18,65</t>
+          <t>13,41; 17,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,59</t>
+          <t>7,45; 10,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,69</t>
+          <t>10,93; 14,59</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,53</t>
+          <t>5,06; 7,5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,85</t>
+          <t>9,45; 12,14</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,98</t>
+          <t>5,25; 6,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,02</t>
+          <t>6,28; 8,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,97</t>
+          <t>5,26; 6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,65</t>
+          <t>5,25; 6,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,45</t>
+          <t>8,41; 10,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,52; 15,99</t>
+          <t>13,61; 15,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,03; 13,42</t>
+          <t>10,96; 13,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,03</t>
+          <t>10,84; 12,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,38</t>
+          <t>7,11; 8,48</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,18; 11,71</t>
+          <t>10,2; 11,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,58; 9,9</t>
+          <t>8,5; 9,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,17</t>
+          <t>8,34; 9,62</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10910</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>17957</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19017; 39135</t>
+          <t>19480; 39101</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20764; 41254</t>
+          <t>21794; 43028</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35942; 61625</t>
+          <t>35995; 60824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3431; 15864</t>
+          <t>2723; 13020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21771; 43848</t>
+          <t>21027; 42808</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48729; 76374</t>
+          <t>48242; 77562</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60074; 90470</t>
+          <t>59294; 89924</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6458; 16862</t>
+          <t>6775; 16670</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46502; 75045</t>
+          <t>43782; 74362</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76416; 112638</t>
+          <t>75190; 113616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103044; 141241</t>
+          <t>104379; 143640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12138; 27210</t>
+          <t>12130; 25427</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39737</t>
+          <t>40363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56263</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95999</t>
+          <t>99305</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30028; 54816</t>
+          <t>29384; 55417</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28324; 55310</t>
+          <t>28723; 55565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7854; 23662</t>
+          <t>8316; 23629</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27187; 58071</t>
+          <t>29075; 57784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60335; 93561</t>
+          <t>61587; 91850</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62880; 97674</t>
+          <t>63793; 96833</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37920; 63879</t>
+          <t>35916; 63743</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45821; 69572</t>
+          <t>46276; 72649</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98527; 139048</t>
+          <t>98843; 139331</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100639; 143590</t>
+          <t>101214; 142748</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48642; 79793</t>
+          <t>48825; 82260</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78900; 115647</t>
+          <t>81425; 120199</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45165</t>
+          <t>48080</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3678; 17017</t>
+          <t>2922; 14482</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10008; 26910</t>
+          <t>9814; 26705</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3006; 12899</t>
+          <t>2989; 13718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10858; 24320</t>
+          <t>11388; 26730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7024; 22353</t>
+          <t>7146; 21755</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26289; 50486</t>
+          <t>26781; 50251</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11580; 28763</t>
+          <t>11483; 28853</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22035; 37702</t>
+          <t>22311; 39930</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12314; 29868</t>
+          <t>12598; 30069</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41326; 70753</t>
+          <t>40084; 68009</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16864; 36185</t>
+          <t>16032; 36903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35618; 56188</t>
+          <t>38555; 60111</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43094</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61557</t>
+          <t>69607</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4605; 17203</t>
+          <t>4840; 17583</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12220; 30206</t>
+          <t>13063; 31408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23599; 45764</t>
+          <t>23793; 45189</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11256; 30000</t>
+          <t>12604; 33042</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19598; 39843</t>
+          <t>19598; 40196</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67414; 100241</t>
+          <t>68305; 100019</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64976; 97642</t>
+          <t>65227; 98160</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27214; 62246</t>
+          <t>37613; 63747</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26442; 50436</t>
+          <t>27118; 51376</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85567; 124153</t>
+          <t>85821; 124072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94535; 136371</t>
+          <t>93592; 135073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44416; 82225</t>
+          <t>54679; 88727</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>25889</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7874; 20988</t>
+          <t>7683; 20407</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5251; 18258</t>
+          <t>5249; 18660</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4922; 17021</t>
+          <t>4944; 16684</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2851; 9798</t>
+          <t>2937; 10102</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8080; 24266</t>
+          <t>9041; 24617</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29131; 52860</t>
+          <t>29248; 53056</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10216; 26769</t>
+          <t>9854; 24403</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15027; 26708</t>
+          <t>15342; 26695</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19679; 40276</t>
+          <t>19599; 39471</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38152; 64026</t>
+          <t>38151; 65840</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17857; 39438</t>
+          <t>17193; 37818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19442; 32906</t>
+          <t>20068; 33603</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37049</t>
+          <t>36824</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>878; 8586</t>
+          <t>936; 9132</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13868; 33110</t>
+          <t>14401; 34445</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11450; 28655</t>
+          <t>11953; 29378</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9816; 22299</t>
+          <t>9350; 21995</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7206; 21196</t>
+          <t>6500; 20972</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22480; 43232</t>
+          <t>22458; 43255</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27778; 53284</t>
+          <t>27333; 51897</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15971; 28424</t>
+          <t>16192; 29351</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9129; 25032</t>
+          <t>9713; 25155</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42703; 69411</t>
+          <t>40925; 68886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44131; 74585</t>
+          <t>44001; 74756</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28539; 47585</t>
+          <t>28946; 46193</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>60411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>98356</t>
+          <t>118166</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>154020</t>
+          <t>178577</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24653; 47980</t>
+          <t>23854; 46951</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22361; 46791</t>
+          <t>22556; 47551</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31344; 58810</t>
+          <t>30798; 58943</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41095; 76524</t>
+          <t>44697; 81459</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53491; 83488</t>
+          <t>53654; 82284</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41081; 71209</t>
+          <t>42377; 72257</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71268; 107942</t>
+          <t>70443; 107832</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47526; 138093</t>
+          <t>99248; 138123</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>84836; 121550</t>
+          <t>83683; 121957</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>71194; 109064</t>
+          <t>70722; 108466</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110681; 155345</t>
+          <t>109810; 156134</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94151; 190111</t>
+          <t>156581; 206815</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40337</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>115910</t>
+          <t>128691</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>156247</t>
+          <t>174880</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47180; 77524</t>
+          <t>47339; 77227</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51950; 89055</t>
+          <t>54196; 87199</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21806; 42576</t>
+          <t>21752; 44290</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18381; 61059</t>
+          <t>34584; 60926</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60741; 94242</t>
+          <t>60731; 93088</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>111715; 156397</t>
+          <t>111313; 154168</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51524; 84339</t>
+          <t>50624; 85509</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>99945; 133757</t>
+          <t>111372; 147547</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>116097; 161818</t>
+          <t>113772; 158199</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>176028; 235362</t>
+          <t>175086; 233685</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>80192; 120904</t>
+          <t>81243; 120368</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>96040; 194995</t>
+          <t>153973; 197787</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>213109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>593991</t>
+          <t>651118</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>171962; 228714</t>
+          <t>171921; 227118</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>211723; 274717</t>
+          <t>214993; 280066</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>179888; 236610</t>
+          <t>178431; 235824</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>150804; 230107</t>
+          <t>185392; 243544</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>285475; 353205</t>
+          <t>284255; 353412</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>480889; 568669</t>
+          <t>483844; 565020</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>390919; 475836</t>
+          <t>388455; 477619</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>323034; 440327</t>
+          <t>404522; 472033</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>475327; 557935</t>
+          <t>473518; 564186</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>710869; 817586</t>
+          <t>711750; 820954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>595029; 687165</t>
+          <t>589503; 686955</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>514146; 652784</t>
+          <t>605652; 698833</t>
         </is>
       </c>
     </row>
